--- a/data/Jharkhand/Dhanbad/Dhanbad_Schools.xlsx
+++ b/data/Jharkhand/Dhanbad/Dhanbad_Schools.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D2"/>
+  <dimension ref="A1:D3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -457,6 +457,28 @@
       <c r="D2" t="inlineStr">
         <is>
           <t>+91 9431392666</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>GD Goenka Public School</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>info@gdgoenkadhanbad.in</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Dhanbad</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Contact School</t>
         </is>
       </c>
     </row>
